--- a/RESULTS/tables/survival_km_external_risk_group_summary.xlsx
+++ b/RESULTS/tables/survival_km_external_risk_group_summary.xlsx
@@ -465,13 +465,13 @@
         <v>2072</v>
       </c>
       <c r="C2" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02557915057915058</v>
+        <v>0.02461389961389961</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03451713919639587</v>
+        <v>0.03647966682910919</v>
       </c>
     </row>
     <row r="3">
@@ -484,13 +484,13 @@
         <v>2072</v>
       </c>
       <c r="C3" t="n">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1790540540540541</v>
+        <v>0.1718146718146718</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1547512114048004</v>
+        <v>0.1560753881931305</v>
       </c>
     </row>
     <row r="4">
@@ -503,13 +503,13 @@
         <v>2072</v>
       </c>
       <c r="C4" t="n">
-        <v>1357</v>
+        <v>1374</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6549227799227799</v>
+        <v>0.6631274131274131</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4858150780200958</v>
+        <v>0.5760523676872253</v>
       </c>
     </row>
   </sheetData>
